--- a/human_validation/judge/kor/judge_D003_S005_P003__claude-sonnet-5_kor.xlsx
+++ b/human_validation/judge/kor/judge_D003_S005_P003__claude-sonnet-5_kor.xlsx
@@ -70,16 +70,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -447,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B34"/>
+  <dimension ref="A1:B26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="90" customWidth="1" min="1" max="1"/>
@@ -561,12 +558,82 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>환자 프로필</t>
+          <t>대화문</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 의사 질문] 안녕하세요, 어서 오세요. 저는 [이름] 선생님입니다. 오늘 어떤 일로 오셨나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 환자 응답] 음, 제가 그냥 가만히 앉아 있어야 할 때도 계속 일어나게 되는 걸 알아차렸어요. 회의 중이나 심지어 저녁 식사 때도, 갑자기 커피를 다시 채워야 할 것 같거나, 유인물을 확인해야 할 것 같거나, 방 뒤쪽으로 가야 할 것 같은 느낌이 들어요. 사실 급한 일은 전혀 없는데도요. 이런 일이 꽤 자주 생겨서 와서 상담을 받아봐야겠다고 생각했어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 의사의 감별진단] 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003) | 주의력결핍 과잉행동장애 (부주의 우세형) (D002)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 의사 질문] 이런 안절부절못함과 움직이고 싶은 충동을 어릴 때부터 느끼셨나요, 아니면 성인이 되고 나서 최근에 시작된 건가요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 환자 응답] 아니요, 새로 생긴 게 아니에요. 어릴 때도, 제 성적표에는 제가 똑똑하다고 적혀 있었지만, 자리에 앉아 있거나 차례를 기다리는 걸 못했어요. 저희 어머니는 제가 열 살이 되기도 전에 책상이랑 연필깎이 사이에 작은 길이 났을 거라고 농담하곤 하셨어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 의사의 감별진단] 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003) | 주의력결핍 과잉행동장애 (부주의 우세형) (D002)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 의사 질문] 안절부절못하는 것 외에, 일에 집중하기 어렵거나, 하던 일을 놓치거나, 집중하려고 해도 세부사항을 깜빡하시는 경우가 자주 있으신가요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 환자 응답] 그게 저한테 큰 문제라고는 잘 모르겠어요. 그러니까, 누구나 가끔 서류를 잃어버리긴 하잖아요. 근데 제가 특별히 건망증이 심하거나 집중하려고 할 때 집중을 못 한다고 느낀 적은 딱히 없어요. 그보다는 일어나서 움직여야 할 것 같은 느낌 쪽이에요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 의사의 감별진단] 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003) | 배제됨: 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>최종 진단 및 진단 체크리스트</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
         <is>
           <t>진단명: 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003)
 인구통계: 성별 여성 / 나이 60 / 직업상태 secondary school teacher / 최종학력 대학원 졸업
@@ -575,140 +642,38 @@
 증상 지속 기간: 8 months
 추가 요건: Onset prior to age 12 years
 주호소 증상 코드: S011
-배경 서술: 이달미스의 막내가 대학에 진학하기 위해 사우스캐롤라이나를 떠난 후, 그녀는 조용해진 저녁 시간을 스페인어과 부가 프로젝트, 문화센터 워크숍, 소프트볼, 독서 모임, 지역 행사용 음식 준비 등으로 채우기 시작했다. 이후 8개월 동안, 새로 생긴 빈 둥지 일정은 그동안 육아와 엄격한 계획 관리로 눌러왔던 안절부절못하는 성향을 드러냈다. 그녀는 교직원 회의 중 자리에 앉아 있기가 점점 어려워졌고, 함께하는 활동 중 조용히 있는 것과, 그룹 토론에서 자기 차례를 기다리는 것이 힘들어졌다. 장애는 눈에 띄었지만 제한적인 수준이었다. 동료들은 교육과정 회의 중 그녀가 서성이는 것을 놀렸고, 독서 모임에서는 그녀가 지나치게 자주 끼어든다고 불평했으며, 남편은 원래 편안해야 할 저녁 시간에 그녀가 끊임없이 움직이는 것을 알아차렸다. 이달미스는 성인 ADHD에 관한 전문성 개발 세미나를 듣고 이 패턴이 학교, 가정, 지역사회 전반에 걸쳐 지속적으로 나타난다는 것을 깨달은 후, 스스로 평가를 요청했다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>대화문</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 의사 질문] 안녕하세요, 어서 오세요. 저는 [이름] 선생님입니다. 오늘 어떤 일로 오셨나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 환자 응답] 음, 제가 그냥 가만히 앉아 있어야 할 때도 계속 일어나게 되는 걸 알아차렸어요. 회의 중이나 심지어 저녁 식사 때도, 갑자기 커피를 다시 채워야 할 것 같거나, 유인물을 확인해야 할 것 같거나, 방 뒤쪽으로 가야 할 것 같은 느낌이 들어요. 사실 급한 일은 전혀 없는데도요. 이런 일이 꽤 자주 생겨서 와서 상담을 받아봐야겠다고 생각했어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="B20" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 의사의 감별진단] 중간확률: 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003) | 저확률: 주의력결핍 과잉행동장애 (부주의 우세형) (D002)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 의사 질문] 이런 안절부절못함과 움직이고 싶은 충동을 어릴 때부터 느끼셨나요, 아니면 성인이 되고 나서 최근에 시작된 건가요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 환자 응답] 아니요, 새로 생긴 게 아니에요. 어릴 때도, 제 성적표에는 제가 똑똑하다고 적혀 있었지만, 자리에 앉아 있거나 차례를 기다리는 걸 못했어요. 저희 어머니는 제가 열 살이 되기도 전에 책상이랑 연필깎이 사이에 작은 길이 났을 거라고 농담하곤 하셨어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 의사의 감별진단] 중간확률: 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003) | 저확률: 주의력결핍 과잉행동장애 (부주의 우세형) (D002)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="B24" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 의사 질문] 안절부절못하는 것 외에, 일에 집중하기 어렵거나, 하던 일을 놓치거나, 집중하려고 해도 세부사항을 깜빡하시는 경우가 자주 있으신가요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 환자 응답] 그게 저한테 큰 문제라고는 잘 모르겠어요. 그러니까, 누구나 가끔 서류를 잃어버리긴 하잖아요. 근데 제가 특별히 건망증이 심하거나 집중하려고 할 때 집중을 못 한다고 느낀 적은 딱히 없어요. 그보다는 일어나서 움직여야 할 것 같은 느낌 쪽이에요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
+배경 서술: 이달미스의 막내가 대학에 진학하기 위해 사우스캐롤라이나를 떠난 후, 그녀는 조용해진 저녁 시간을 스페인어과 부가 프로젝트, 문화센터 워크숍, 소프트볼, 독서 모임, 지역 행사용 음식 준비 등으로 채우기 시작했다. 이후 8개월 동안, 새로 생긴 빈 둥지 일정은 그동안 육아와 엄격한 계획 관리로 눌러왔던 안절부절못하는 성향을 드러냈다. 그녀는 교직원 회의 중 자리에 앉아 있기가 점점 어려워졌고, 함께하는 활동 중 조용히 있는 것과, 그룹 토론에서 자기 차례를 기다리는 것이 힘들어졌다. 장애는 눈에 띄었지만 제한적인 수준이었다. 동료들은 교육과정 회의 중 그녀가 서성이는 것을 놀렸고, 독서 모임에서는 그녀가 지나치게 자주 끼어든다고 불평했으며, 남편은 원래 편안해야 할 저녁 시간에 그녀가 끊임없이 움직이는 것을 알아차렸다. 이달미스는 성인 ADHD에 관한 전문성 개발 세미나를 듣고 이 패턴이 학교, 가정, 지역사회 전반에 걸쳐 지속적으로 나타난다는 것을 깨달은 후, 스스로 평가를 요청했다.
+표집된 증상 목록:
+  - S010 손발 꼼지락거림: 손발을 가만두지 못하고 두드리거나 자리에서 꼼지락거리는 경우가 잦다.
+  - S011 자리 이탈: 가만히 앉아 있어야 하는 상황에서 자주 자리를 떠난다.
+  - S013 조용한 활동 곤란: 여가 활동을 조용히 하지 못하는 경우가 잦다.
+  - S014 끊임없는 활동성: 마치 '모터가 달린 것처럼' 끊임없이 활동한다.
+  - S015 과도한 말하기: 지나치게 말을 많이 하는 경우가 잦다.
+  - S018 끼어들기/방해: 다른 사람의 대화나 활동에 자주 끼어들거나 방해한다(예: 대화, 게임, 활동에 불쑥 끼어듦).</t>
+        </is>
+      </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>[3번째 턴 · 의사의 감별진단] 중간확률: 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003) | 배제됨: 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002)</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>최종 진단 및 진단 체크리스트</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="6" t="inlineStr">
-        <is>
-          <t>의사의 최종 진단: 주의력결핍 과잉행동장애 (부주의 우세형) (D002, ICD: F90.0)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="5" t="inlineStr">
-        <is>
-          <t>지속 기간 요건 — 점수: 1.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="5" t="inlineStr">
-        <is>
-          <t>기능적 손상 요건 — 점수: 1.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="5" t="inlineStr">
-        <is>
-          <t>추가 요건 — 점수: 1.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="5" t="inlineStr">
-        <is>
-          <t>체크리스트 그룹: inattention (관계=include, 요구개수=5, 충족개수=0, 커버리지=0.0)
-  확인된 근거: (없음)
-  누락: 세부사항 부주의 실수: 세부적인 것에 주의를 기울이지 못하거나 부주의한 실수를 자주 한다.; 지속적 주의 유지 곤란: 과제나 놀이 활동에서 주의를 지속하는 데 자주 어려움을 겪는다.; 경청 곤란: 직접 말을 걸어도 듣지 않는 것처럼 보이는 경우가 잦다.; 지시 이행 곤란: 지시를 끝까지 따르지 못하고 학업, 집안일, 직장 업무를 제대로 마치지 못하는 경우가 잦다.; 조직화 곤란: 과제와 활동을 체계적으로 조직하는 데 자주 어려움을 겪는다.; 지속적 정신적 노력 회피: 지속적인 정신적 노력을 요하는 과제를 자주 피하거나 싫어하거나 꺼린다.; 물건 분실: 과제나 활동에 필요한 물건을 자주 잃어버린다.; 산만함: 외부 자극에 의해 쉽게 주의가 분산된다(청소년 후기 및 성인의 경우 관련 없는 생각도 포함될 수 있다).; 일상 활동 망각: 일상 활동에서 자주 잊어버린다(예: 집안일, 심부름, 성인의 경우 전화 회신, 청구서 납부, 약속 지키기 등).</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="5" t="inlineStr">
-        <is>
-          <t>체크리스트 그룹: hyperactivity_impulsivity (관계=must_include, 요구개수=5, 충족개수=2, 커버리지=0.4)
-  확인된 근거: 자리 이탈: 가만히 앉아 있어야 하는 상황에서 자주 자리를 떠난다.; 차례 기다리기 곤란: 차례를 기다리는 데 자주 어려움을 겪는다.
-  누락: 손발 꼼지락거림: 손발을 가만두지 못하고 두드리거나 자리에서 꼼지락거리는 경우가 잦다.; 안절부절못함: 부적절한 상황에서 자주 뛰어다니거나 기어오른다(청소년/성인의 경우 안절부절못하는 느낌으로 제한될 수 있다).; 조용한 활동 곤란: 여가 활동을 조용히 하지 못하는 경우가 잦다.; 끊임없는 활동성: 마치 '모터가 달린 것처럼' 끊임없이 활동한다.; 과도한 말하기: 지나치게 말을 많이 하는 경우가 잦다.; 성급한 대답: 질문이 끝나기도 전에 불쑥 대답해버리는 경우가 잦다.; 끼어들기/방해: 다른 사람의 대화나 활동에 자주 끼어들거나 방해한다(예: 대화, 게임, 활동에 불쑥 끼어듦).</t>
+          <t>의사의 최종 진단: 주의력결핍 과잉행동장애 (부주의 우세형) (D002, ICD: F90.0)
+지속 기간 요건: 있음
+기능적 손상 요건: 있음
+추가 요건: 있음
+체크리스트 그룹: inattention (관계=include, 요구개수=5, 충족개수=0, 커버리지=0.0)
+확인된 근거:
+  (없음)
+체크리스트 그룹: hyperactivity_impulsivity (관계=must_include, 요구개수=5, 충족개수=2, 커버리지=0.4)
+확인된 근거:
+  - 자리 이탈: 가만히 앉아 있어야 하는 상황에서 자주 자리를 떠난다.
+  - 차례 기다리기 곤란: 차례를 기다리는 데 자주 어려움을 겪는다.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="4">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="A25:B25"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/human_validation/judge/kor/judge_D003_S005_P003__claude-sonnet-5_kor.xlsx
+++ b/human_validation/judge/kor/judge_D003_S005_P003__claude-sonnet-5_kor.xlsx
@@ -628,6 +628,11 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
+          <t>환자 증상 프로필</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
           <t>최종 진단 및 진단 체크리스트</t>
         </is>
       </c>
@@ -669,11 +674,10 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="3">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A25:B25"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/human_validation/judge/kor/judge_D003_S005_P003__claude-sonnet-5_kor.xlsx
+++ b/human_validation/judge/kor/judge_D003_S005_P003__claude-sonnet-5_kor.xlsx
@@ -458,6 +458,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -472,7 +473,7 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>0.5833</v>
+        <v>0.3889</v>
       </c>
     </row>
     <row r="5">
@@ -482,7 +483,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>0.5833</v>
+        <v>0.3889</v>
       </c>
     </row>
     <row r="6">
@@ -502,7 +503,7 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -555,6 +556,7 @@
         <v>0.75</v>
       </c>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
